--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -819,6 +824,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55301870</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -956,6 +966,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55301885</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1068,6 +1083,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128891184</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1187,6 +1207,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/178627</t>
         </is>
       </c>
     </row>
@@ -1299,6 +1324,11 @@
           <t>Dalaflorans databas</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62590927</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1433,6 +1463,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119370949</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1567,6 +1602,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371068</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1672,6 +1712,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67270180</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1779,6 +1824,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135077362</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1910,6 +1960,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119879735</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2043,6 +2098,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67756766</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2177,6 +2237,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87985131</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2306,6 +2371,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820384</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2440,6 +2510,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79671722</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2569,6 +2644,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480026</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2703,6 +2783,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127833476</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2832,6 +2917,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820355</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2970,6 +3060,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67756774</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3104,6 +3199,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111616228</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3238,6 +3338,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95858489</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3359,6 +3464,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480091</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3493,6 +3603,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79671674</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3614,6 +3729,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67756510</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3748,6 +3868,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79671725</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3878,6 +4003,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67756544</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4004,6 +4134,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95858514</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4130,6 +4265,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95858606</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4264,6 +4404,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119879949</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4390,6 +4535,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128478067</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4519,6 +4669,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480099</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4645,6 +4800,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119879748</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4770,6 +4930,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67756782</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4904,6 +5069,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119879940</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5043,6 +5213,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95858510</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5152,6 +5327,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104268278</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5286,6 +5466,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95858876</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5420,6 +5605,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95858879</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5554,6 +5744,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111616223</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5683,6 +5878,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820397</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5817,6 +6017,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128478071</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5947,6 +6152,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67756539</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6081,6 +6291,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95858601</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6220,6 +6435,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119879938</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6351,6 +6571,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127833352</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6485,6 +6710,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119879962</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6594,6 +6824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121225539</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6699,8 +6934,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78740010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -1723,7 +1723,7 @@
         <v>135077362</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1723,7 +1723,7 @@
         <v>135077362</v>
       </c>
       <c r="B10" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67756544</v>
+        <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93209</v>
+        <v>93340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3887,39 +3887,48 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo Gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523255</v>
+        <v>523494</v>
       </c>
       <c r="R26" t="n">
-        <v>6657390</v>
+        <v>6657512</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3943,17 +3952,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>massor</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3968,50 +3972,30 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>gruvområde</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67756544</t>
+          <t>https://artportalen.se/Sighting/135679638</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95858514</v>
+        <v>67756544</v>
       </c>
       <c r="B27" t="n">
         <v>93209</v>
@@ -4042,20 +4026,19 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tombo gruvorna, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523225</v>
+        <v>523255</v>
       </c>
       <c r="R27" t="n">
-        <v>6657366</v>
+        <v>6657390</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4079,12 +4062,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>massor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4104,7 +4092,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>kalkmarksskog i gruvområde</t>
+          <t>gruvområde</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4136,13 +4124,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858514</t>
+          <t>https://artportalen.se/Sighting/67756544</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95858606</v>
+        <v>95858514</v>
       </c>
       <c r="B28" t="n">
         <v>93209</v>
@@ -4180,13 +4168,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523248</v>
+        <v>523225</v>
       </c>
       <c r="R28" t="n">
-        <v>6657389</v>
+        <v>6657366</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4267,13 +4255,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858606</t>
+          <t>https://artportalen.se/Sighting/95858514</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119879949</v>
+        <v>95858606</v>
       </c>
       <c r="B29" t="n">
         <v>93209</v>
@@ -4301,31 +4289,23 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tombo gruva, Dlr</t>
+          <t>Tombo gruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523242</v>
+        <v>523248</v>
       </c>
       <c r="R29" t="n">
-        <v>6657390</v>
+        <v>6657389</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4349,12 +4329,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4369,12 +4349,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Lågörtblandskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmarksskog i gruvområde</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4406,13 +4386,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879949</t>
+          <t>https://artportalen.se/Sighting/95858606</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128478067</v>
+        <v>119879949</v>
       </c>
       <c r="B30" t="n">
         <v>93209</v>
@@ -4440,23 +4420,31 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523234</v>
+        <v>523242</v>
       </c>
       <c r="R30" t="n">
-        <v>6657385</v>
+        <v>6657390</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4480,12 +4468,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4500,12 +4488,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Lågörtblandskog</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkmark. Gruvområde.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4531,56 +4519,48 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128478067</t>
+          <t>https://artportalen.se/Sighting/119879949</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96480099</v>
+        <v>128478067</v>
       </c>
       <c r="B31" t="n">
-        <v>89143</v>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4405</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -4589,10 +4569,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523252</v>
+        <v>523234</v>
       </c>
       <c r="R31" t="n">
-        <v>6657389</v>
+        <v>6657385</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4619,12 +4599,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4642,6 +4622,11 @@
           <t>Lågörtbarrskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkmark. Gruvområde.</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4671,57 +4656,65 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96480099</t>
+          <t>https://artportalen.se/Sighting/128478067</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119879748</v>
+        <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>91893</v>
+        <v>93358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4660</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo Gruva, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523392</v>
+        <v>523503</v>
       </c>
       <c r="R32" t="n">
-        <v>6657470</v>
+        <v>6657486</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4745,12 +4738,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 mycel</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4765,53 +4763,48 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Lågörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>blottad ved på grov levande asp # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879748</t>
+          <t>https://artportalen.se/Sighting/135679621</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67756782</v>
+        <v>96480099</v>
       </c>
       <c r="B33" t="n">
-        <v>92869</v>
+        <v>89143</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4819,36 +4812,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>4405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523188</v>
+        <v>523252</v>
       </c>
       <c r="R33" t="n">
-        <v>6657373</v>
+        <v>6657389</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4875,12 +4877,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4898,11 +4900,6 @@
           <t>Lågörtbarrskog</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>gruvområde</t>
-        </is>
-      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4926,71 +4923,63 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67756782</t>
+          <t>https://artportalen.se/Sighting/96480099</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119879940</v>
+        <v>119879748</v>
       </c>
       <c r="B34" t="n">
-        <v>90522</v>
+        <v>91893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4962</v>
+        <v>4660</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tombo gruva, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523242</v>
+        <v>523392</v>
       </c>
       <c r="R34" t="n">
-        <v>6657390</v>
+        <v>6657470</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5044,17 +5033,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>blottad ved på grov levande asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5071,65 +5060,56 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879940</t>
+          <t>https://artportalen.se/Sighting/119879748</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>95858510</v>
+        <v>67756782</v>
       </c>
       <c r="B35" t="n">
-        <v>91409</v>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5741</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tombo gruvorna, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523225</v>
+        <v>523188</v>
       </c>
       <c r="R35" t="n">
-        <v>6657366</v>
+        <v>6657373</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5153,17 +5133,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>övermogna</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5183,7 +5158,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>kalkmarksskog i gruvområde</t>
+          <t>gruvområde</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5215,16 +5190,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858510</t>
+          <t>https://artportalen.se/Sighting/67756782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104268278</v>
+        <v>119879940</v>
       </c>
       <c r="B36" t="n">
-        <v>91409</v>
+        <v>90522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5232,21 +5207,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5741</v>
+        <v>4962</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5263,17 +5238,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tombo gruvorna, Dlr</t>
+          <t>Tombo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523180</v>
+        <v>523242</v>
       </c>
       <c r="R36" t="n">
-        <v>6657372</v>
+        <v>6657390</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5297,12 +5272,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5315,6 +5290,31 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5329,38 +5329,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104268278</t>
+          <t>https://artportalen.se/Sighting/119879940</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>95858876</v>
+        <v>95858510</v>
       </c>
       <c r="B37" t="n">
-        <v>91435</v>
+        <v>91409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>5741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523180</v>
+        <v>523225</v>
       </c>
       <c r="R37" t="n">
-        <v>6657372</v>
+        <v>6657366</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -5419,6 +5419,11 @@
           <t>2021-09-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>övermogna</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5468,16 +5473,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858876</t>
+          <t>https://artportalen.se/Sighting/95858510</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95858879</v>
+        <v>104268278</v>
       </c>
       <c r="B38" t="n">
-        <v>91443</v>
+        <v>91409</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5485,26 +5490,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5754</v>
+        <v>5741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5520,10 +5525,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523183</v>
+        <v>523180</v>
       </c>
       <c r="R38" t="n">
-        <v>6657350</v>
+        <v>6657372</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5550,12 +5555,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5568,31 +5573,6 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>kalkmarksskog i gruvområde</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
@@ -5607,43 +5587,43 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858879</t>
+          <t>https://artportalen.se/Sighting/104268278</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111616223</v>
+        <v>95858876</v>
       </c>
       <c r="B39" t="n">
-        <v>91443</v>
+        <v>91435</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5754</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5655,17 +5635,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo gruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523269</v>
+        <v>523180</v>
       </c>
       <c r="R39" t="n">
-        <v>6657405</v>
+        <v>6657372</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5689,12 +5669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5709,12 +5689,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmarksskog i gruvområde</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5740,19 +5720,19 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111616223</t>
+          <t>https://artportalen.se/Sighting/95858876</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127820397</v>
+        <v>95858879</v>
       </c>
       <c r="B40" t="n">
         <v>91443</v>
@@ -5782,7 +5762,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5794,17 +5774,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo gruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523261</v>
+        <v>523183</v>
       </c>
       <c r="R40" t="n">
-        <v>6657398</v>
+        <v>6657350</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5828,12 +5808,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5846,9 +5826,14 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkmarkskog</t>
+          <t>kalkmarksskog i gruvområde</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5869,24 +5854,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127820397</t>
+          <t>https://artportalen.se/Sighting/95858879</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128478071</v>
+        <v>111616223</v>
       </c>
       <c r="B41" t="n">
         <v>91443</v>
@@ -5916,7 +5901,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5932,10 +5917,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523270</v>
+        <v>523269</v>
       </c>
       <c r="R41" t="n">
-        <v>6657402</v>
+        <v>6657405</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5962,12 +5947,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5982,12 +5967,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkmark. Gruvområde.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -6019,16 +6004,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128478071</t>
+          <t>https://artportalen.se/Sighting/111616223</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>67756539</v>
+        <v>127820397</v>
       </c>
       <c r="B42" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6036,39 +6021,48 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523255</v>
+        <v>523261</v>
       </c>
       <c r="R42" t="n">
-        <v>6657390</v>
+        <v>6657398</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6092,17 +6086,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>massor</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6115,14 +6104,9 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>gruvområde</t>
+          <t>Kalkmarkskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6143,27 +6127,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67756539</t>
+          <t>https://artportalen.se/Sighting/127820397</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>95858601</v>
+        <v>128478071</v>
       </c>
       <c r="B43" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6171,26 +6155,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6202,14 +6186,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tombo gruvorna, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523248</v>
+        <v>523270</v>
       </c>
       <c r="R43" t="n">
-        <v>6657389</v>
+        <v>6657402</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6236,12 +6220,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6261,7 +6245,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>kalkmarksskog i gruvområde</t>
+          <t>Kalkmark. Gruvområde.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6287,19 +6271,19 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858601</t>
+          <t>https://artportalen.se/Sighting/128478071</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119879938</v>
+        <v>67756539</v>
       </c>
       <c r="B44" t="n">
         <v>93233</v>
@@ -6327,31 +6311,22 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tombo gruva, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523242</v>
+        <v>523255</v>
       </c>
       <c r="R44" t="n">
         <v>6657390</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6375,17 +6350,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>minst 50 ex</t>
+          <t>massor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6400,12 +6375,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Lågörtblandskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>gruvområde</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6437,13 +6412,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879938</t>
+          <t>https://artportalen.se/Sighting/67756539</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127833352</v>
+        <v>95858601</v>
       </c>
       <c r="B45" t="n">
         <v>93233</v>
@@ -6471,20 +6446,28 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo gruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523243</v>
+        <v>523248</v>
       </c>
       <c r="R45" t="n">
-        <v>6657391</v>
+        <v>6657389</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6511,17 +6494,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>flera mycel</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6536,12 +6514,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmarksskog i gruvområde</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6567,44 +6545,44 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127833352</t>
+          <t>https://artportalen.se/Sighting/95858601</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119879962</v>
+        <v>119879938</v>
       </c>
       <c r="B46" t="n">
-        <v>87297</v>
+        <v>93233</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003296</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6614,7 +6592,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -6625,10 +6603,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523260</v>
+        <v>523242</v>
       </c>
       <c r="R46" t="n">
-        <v>6657396</v>
+        <v>6657390</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6663,6 +6641,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>minst 50 ex</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6712,66 +6695,57 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879962</t>
+          <t>https://artportalen.se/Sighting/119879938</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121225539</v>
+        <v>127833352</v>
       </c>
       <c r="B47" t="n">
-        <v>57141</v>
+        <v>93233</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tolvsboberg, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520508</v>
+        <v>523243</v>
       </c>
       <c r="R47" t="n">
-        <v>6656363</v>
+        <v>6657391</v>
       </c>
       <c r="S47" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6790,17 +6764,22 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Norrbärke</t>
+          <t>Söderbärke</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>flera mycel</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6809,79 +6788,108 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Krister Fredriksson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Krister Fredriksson</t>
+          <t>Janolof Hermansson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121225539</t>
+          <t>https://artportalen.se/Sighting/127833352</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>78740010</v>
+        <v>119879962</v>
       </c>
       <c r="B48" t="n">
-        <v>56522</v>
+        <v>87297</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>206004</v>
+        <v>6003296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tolvsboberg, Dlr</t>
+          <t>Tombo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520508</v>
+        <v>523260</v>
       </c>
       <c r="R48" t="n">
-        <v>6656363</v>
+        <v>6657396</v>
       </c>
       <c r="S48" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6900,17 +6908,17 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Norrbärke</t>
+          <t>Söderbärke</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2019-07-04</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2019-07-04</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6919,22 +6927,272 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Krister Fredriksson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Krister Fredriksson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119879962</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121225539</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tolvsboberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>520508</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6656363</v>
+      </c>
+      <c r="S49" t="n">
+        <v>100</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Krister Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Krister Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121225539</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>78740010</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tolvsboberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>520508</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6656363</v>
+      </c>
+      <c r="S50" t="n">
+        <v>100</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Krister Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Krister Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/78740010</t>
         </is>
@@ -6989,6 +7247,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3876,10 +3876,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67756544</v>
+        <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93209</v>
+        <v>93345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3887,39 +3887,48 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo Gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523255</v>
+        <v>523494</v>
       </c>
       <c r="R26" t="n">
-        <v>6657390</v>
+        <v>6657512</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3943,17 +3952,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>massor</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3968,50 +3972,30 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>gruvområde</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67756544</t>
+          <t>https://artportalen.se/Sighting/135679638</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95858514</v>
+        <v>67756544</v>
       </c>
       <c r="B27" t="n">
         <v>93209</v>
@@ -4042,20 +4026,19 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tombo gruvorna, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523225</v>
+        <v>523255</v>
       </c>
       <c r="R27" t="n">
-        <v>6657366</v>
+        <v>6657390</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4079,12 +4062,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>massor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4104,7 +4092,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>kalkmarksskog i gruvområde</t>
+          <t>gruvområde</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4136,13 +4124,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858514</t>
+          <t>https://artportalen.se/Sighting/67756544</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95858606</v>
+        <v>95858514</v>
       </c>
       <c r="B28" t="n">
         <v>93209</v>
@@ -4180,13 +4168,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523248</v>
+        <v>523225</v>
       </c>
       <c r="R28" t="n">
-        <v>6657389</v>
+        <v>6657366</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4267,13 +4255,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858606</t>
+          <t>https://artportalen.se/Sighting/95858514</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119879949</v>
+        <v>95858606</v>
       </c>
       <c r="B29" t="n">
         <v>93209</v>
@@ -4301,31 +4289,23 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tombo gruva, Dlr</t>
+          <t>Tombo gruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523242</v>
+        <v>523248</v>
       </c>
       <c r="R29" t="n">
-        <v>6657390</v>
+        <v>6657389</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4349,12 +4329,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4369,12 +4349,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Lågörtblandskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmarksskog i gruvområde</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4406,13 +4386,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879949</t>
+          <t>https://artportalen.se/Sighting/95858606</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128478067</v>
+        <v>119879949</v>
       </c>
       <c r="B30" t="n">
         <v>93209</v>
@@ -4440,23 +4420,31 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523234</v>
+        <v>523242</v>
       </c>
       <c r="R30" t="n">
-        <v>6657385</v>
+        <v>6657390</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4480,12 +4468,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4500,12 +4488,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Lågörtblandskog</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkmark. Gruvområde.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4531,56 +4519,48 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128478067</t>
+          <t>https://artportalen.se/Sighting/119879949</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96480099</v>
+        <v>128478067</v>
       </c>
       <c r="B31" t="n">
-        <v>89143</v>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4405</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -4589,10 +4569,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523252</v>
+        <v>523234</v>
       </c>
       <c r="R31" t="n">
-        <v>6657389</v>
+        <v>6657385</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4619,12 +4599,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4642,6 +4622,11 @@
           <t>Lågörtbarrskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkmark. Gruvområde.</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4671,57 +4656,65 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96480099</t>
+          <t>https://artportalen.se/Sighting/128478067</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119879748</v>
+        <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>91893</v>
+        <v>93363</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4660</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo Gruva, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523392</v>
+        <v>523503</v>
       </c>
       <c r="R32" t="n">
-        <v>6657470</v>
+        <v>6657486</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4745,12 +4738,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 mycel</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4765,53 +4763,48 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Lågörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>blottad ved på grov levande asp # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879748</t>
+          <t>https://artportalen.se/Sighting/135679621</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67756782</v>
+        <v>96480099</v>
       </c>
       <c r="B33" t="n">
-        <v>92869</v>
+        <v>89143</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4819,36 +4812,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>4405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523188</v>
+        <v>523252</v>
       </c>
       <c r="R33" t="n">
-        <v>6657373</v>
+        <v>6657389</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4875,12 +4877,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4898,11 +4900,6 @@
           <t>Lågörtbarrskog</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>gruvområde</t>
-        </is>
-      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4926,71 +4923,63 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67756782</t>
+          <t>https://artportalen.se/Sighting/96480099</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119879940</v>
+        <v>119879748</v>
       </c>
       <c r="B34" t="n">
-        <v>90522</v>
+        <v>91893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4962</v>
+        <v>4660</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tombo gruva, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523242</v>
+        <v>523392</v>
       </c>
       <c r="R34" t="n">
-        <v>6657390</v>
+        <v>6657470</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5044,17 +5033,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>blottad ved på grov levande asp # Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5071,65 +5060,56 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879940</t>
+          <t>https://artportalen.se/Sighting/119879748</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>95858510</v>
+        <v>67756782</v>
       </c>
       <c r="B35" t="n">
-        <v>91409</v>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5741</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tombo gruvorna, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523225</v>
+        <v>523188</v>
       </c>
       <c r="R35" t="n">
-        <v>6657366</v>
+        <v>6657373</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5153,17 +5133,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>övermogna</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5183,7 +5158,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>kalkmarksskog i gruvområde</t>
+          <t>gruvområde</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5215,16 +5190,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858510</t>
+          <t>https://artportalen.se/Sighting/67756782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104268278</v>
+        <v>119879940</v>
       </c>
       <c r="B36" t="n">
-        <v>91409</v>
+        <v>90522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5232,21 +5207,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5741</v>
+        <v>4962</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5263,17 +5238,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tombo gruvorna, Dlr</t>
+          <t>Tombo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523180</v>
+        <v>523242</v>
       </c>
       <c r="R36" t="n">
-        <v>6657372</v>
+        <v>6657390</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5297,12 +5272,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5315,6 +5290,31 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5329,38 +5329,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104268278</t>
+          <t>https://artportalen.se/Sighting/119879940</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>95858876</v>
+        <v>95858510</v>
       </c>
       <c r="B37" t="n">
-        <v>91435</v>
+        <v>91409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>5741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523180</v>
+        <v>523225</v>
       </c>
       <c r="R37" t="n">
-        <v>6657372</v>
+        <v>6657366</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -5419,6 +5419,11 @@
           <t>2021-09-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>övermogna</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5468,16 +5473,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858876</t>
+          <t>https://artportalen.se/Sighting/95858510</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95858879</v>
+        <v>104268278</v>
       </c>
       <c r="B38" t="n">
-        <v>91443</v>
+        <v>91409</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5485,26 +5490,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5754</v>
+        <v>5741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5520,10 +5525,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523183</v>
+        <v>523180</v>
       </c>
       <c r="R38" t="n">
-        <v>6657350</v>
+        <v>6657372</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5550,12 +5555,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5568,31 +5573,6 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>kalkmarksskog i gruvområde</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
@@ -5607,43 +5587,43 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858879</t>
+          <t>https://artportalen.se/Sighting/104268278</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111616223</v>
+        <v>95858876</v>
       </c>
       <c r="B39" t="n">
-        <v>91443</v>
+        <v>91435</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5754</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5655,17 +5635,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo gruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523269</v>
+        <v>523180</v>
       </c>
       <c r="R39" t="n">
-        <v>6657405</v>
+        <v>6657372</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5689,12 +5669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5709,12 +5689,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmarksskog i gruvområde</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5740,19 +5720,19 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111616223</t>
+          <t>https://artportalen.se/Sighting/95858876</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127820397</v>
+        <v>95858879</v>
       </c>
       <c r="B40" t="n">
         <v>91443</v>
@@ -5782,7 +5762,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5794,17 +5774,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo gruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523261</v>
+        <v>523183</v>
       </c>
       <c r="R40" t="n">
-        <v>6657398</v>
+        <v>6657350</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5828,12 +5808,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5846,9 +5826,14 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkmarkskog</t>
+          <t>kalkmarksskog i gruvområde</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5869,24 +5854,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127820397</t>
+          <t>https://artportalen.se/Sighting/95858879</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128478071</v>
+        <v>111616223</v>
       </c>
       <c r="B41" t="n">
         <v>91443</v>
@@ -5916,7 +5901,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5932,10 +5917,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523270</v>
+        <v>523269</v>
       </c>
       <c r="R41" t="n">
-        <v>6657402</v>
+        <v>6657405</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5962,12 +5947,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5982,12 +5967,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkmark. Gruvområde.</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -6019,16 +6004,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128478071</t>
+          <t>https://artportalen.se/Sighting/111616223</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>67756539</v>
+        <v>127820397</v>
       </c>
       <c r="B42" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6036,39 +6021,48 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523255</v>
+        <v>523261</v>
       </c>
       <c r="R42" t="n">
-        <v>6657390</v>
+        <v>6657398</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6092,17 +6086,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>massor</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6115,14 +6104,9 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>gruvområde</t>
+          <t>Kalkmarkskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6143,27 +6127,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67756539</t>
+          <t>https://artportalen.se/Sighting/127820397</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>95858601</v>
+        <v>128478071</v>
       </c>
       <c r="B43" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6171,26 +6155,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6202,14 +6186,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tombo gruvorna, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523248</v>
+        <v>523270</v>
       </c>
       <c r="R43" t="n">
-        <v>6657389</v>
+        <v>6657402</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6236,12 +6220,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6261,7 +6245,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>kalkmarksskog i gruvområde</t>
+          <t>Kalkmark. Gruvområde.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6287,19 +6271,19 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858601</t>
+          <t>https://artportalen.se/Sighting/128478071</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119879938</v>
+        <v>67756539</v>
       </c>
       <c r="B44" t="n">
         <v>93233</v>
@@ -6327,31 +6311,22 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tombo gruva, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523242</v>
+        <v>523255</v>
       </c>
       <c r="R44" t="n">
         <v>6657390</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6375,17 +6350,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>minst 50 ex</t>
+          <t>massor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6400,12 +6375,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Lågörtblandskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>gruvområde</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6437,13 +6412,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879938</t>
+          <t>https://artportalen.se/Sighting/67756539</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127833352</v>
+        <v>95858601</v>
       </c>
       <c r="B45" t="n">
         <v>93233</v>
@@ -6471,20 +6446,28 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tombo gruvor, Dlr</t>
+          <t>Tombo gruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523243</v>
+        <v>523248</v>
       </c>
       <c r="R45" t="n">
-        <v>6657391</v>
+        <v>6657389</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6511,17 +6494,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>flera mycel</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6536,12 +6514,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalkmarksskog i gruvområde</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6567,44 +6545,44 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127833352</t>
+          <t>https://artportalen.se/Sighting/95858601</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119879962</v>
+        <v>119879938</v>
       </c>
       <c r="B46" t="n">
-        <v>87297</v>
+        <v>93233</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003296</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6614,7 +6592,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -6625,10 +6603,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523260</v>
+        <v>523242</v>
       </c>
       <c r="R46" t="n">
-        <v>6657396</v>
+        <v>6657390</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6663,6 +6641,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>minst 50 ex</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6712,66 +6695,57 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119879962</t>
+          <t>https://artportalen.se/Sighting/119879938</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121225539</v>
+        <v>127833352</v>
       </c>
       <c r="B47" t="n">
-        <v>57141</v>
+        <v>93233</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tolvsboberg, Dlr</t>
+          <t>Tombo gruvor, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520508</v>
+        <v>523243</v>
       </c>
       <c r="R47" t="n">
-        <v>6656363</v>
+        <v>6657391</v>
       </c>
       <c r="S47" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6790,17 +6764,22 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Norrbärke</t>
+          <t>Söderbärke</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>flera mycel</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6809,79 +6788,108 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Krister Fredriksson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Krister Fredriksson</t>
+          <t>Janolof Hermansson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121225539</t>
+          <t>https://artportalen.se/Sighting/127833352</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>78740010</v>
+        <v>119879962</v>
       </c>
       <c r="B48" t="n">
-        <v>56522</v>
+        <v>87297</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>206004</v>
+        <v>6003296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tolvsboberg, Dlr</t>
+          <t>Tombo gruva, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520508</v>
+        <v>523260</v>
       </c>
       <c r="R48" t="n">
-        <v>6656363</v>
+        <v>6657396</v>
       </c>
       <c r="S48" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6900,17 +6908,17 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Norrbärke</t>
+          <t>Söderbärke</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2019-07-04</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2019-07-04</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6919,22 +6927,272 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Krister Fredriksson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Krister Fredriksson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119879962</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121225539</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tolvsboberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>520508</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6656363</v>
+      </c>
+      <c r="S49" t="n">
+        <v>100</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Krister Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Krister Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121225539</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>78740010</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tolvsboberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>520508</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6656363</v>
+      </c>
+      <c r="S50" t="n">
+        <v>100</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Krister Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Krister Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/78740010</t>
         </is>
@@ -6989,6 +7247,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -3879,7 +3879,7 @@
         <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>93363</v>
+        <v>93365</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -3879,7 +3879,7 @@
         <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -3879,7 +3879,7 @@
         <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -3879,7 +3879,7 @@
         <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -3879,7 +3879,7 @@
         <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -3879,7 +3879,7 @@
         <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/S 924-2023 artfynd.xlsx
+++ b/artfynd/S 924-2023 artfynd.xlsx
@@ -3879,7 +3879,7 @@
         <v>135679638</v>
       </c>
       <c r="B26" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>135679621</v>
       </c>
       <c r="B32" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
